--- a/Assets/Editor Default Resources/Excel/TransilationData.xlsx
+++ b/Assets/Editor Default Resources/Excel/TransilationData.xlsx
@@ -4,10 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12790"/>
+    <workbookView windowWidth="24750" windowHeight="12790" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="rushTodefence" sheetId="1" r:id="rId1"/>
+    <sheet name="rushToback" sheetId="2" r:id="rId2"/>
+    <sheet name="rushTocheck" sheetId="3" r:id="rId3"/>
+    <sheet name="rushToyuhui" sheetId="4" r:id="rId4"/>
+    <sheet name="backTorush" sheetId="5" r:id="rId5"/>
+    <sheet name="backTodefence" sheetId="6" r:id="rId6"/>
+    <sheet name="backTocheck" sheetId="7" r:id="rId7"/>
+    <sheet name="backToyuhui" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="17">
   <si>
     <t>cmdType</t>
   </si>
@@ -47,10 +54,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>条件1</t>
+    <t>小队击杀数与小队人数之比大于等于0.5</t>
   </si>
   <si>
-    <t>条件2</t>
+    <t>小队击杀数与小队人数之比大于等于0.7</t>
   </si>
   <si>
     <t>条件3</t>
@@ -60,6 +67,24 @@
   </si>
   <si>
     <t>条件5</t>
+  </si>
+  <si>
+    <t>自身血量下降到0.3</t>
+  </si>
+  <si>
+    <t>自身血量下降到0.5</t>
+  </si>
+  <si>
+    <t>遇到迷雾</t>
+  </si>
+  <si>
+    <t>攻击范围内没有敌人</t>
+  </si>
+  <si>
+    <t>当自身生命值上升到90%</t>
+  </si>
+  <si>
+    <t>当自身生命值上升到80%</t>
   </si>
 </sst>
 </file>
@@ -1005,6 +1030,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="38.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1064,7 +1090,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1075,7 +1101,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1088,4 +1114,638 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="24.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="20.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="20.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>